--- a/06_附件资料/表格相关/合并后组织导入数据.xlsx
+++ b/06_附件资料/表格相关/合并后组织导入数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13500"/>
+    <workbookView windowWidth="30720" windowHeight="13044"/>
   </bookViews>
   <sheets>
     <sheet name="组织导入模板" sheetId="1" r:id="rId1"/>
@@ -441,7 +441,8 @@
     <t>新改扩房屋建设工程，水务工程，既有建筑修缮工程，建筑装饰装修工程，既有建筑加装电梯工程，临时建设工程，农民自建房工程，农业设施建设工程，农村地区综合性建设工程</t>
   </si>
   <si>
-    <t>住宅小区公共区域内场所，中心商场,公共图书馆,医院,歌舞厅,工业厂房,独立办公楼,民用机场航站楼,变电站,集体宿舍,寺庙,市场,博物馆,疗养院,录像厅,生产车间,商务公寓,客运车站候车厅,水泵房,宾馆,教堂,沿街商铺,公共展览馆,养老院,放映厅,加工场所,律所,客运码头候船厅,通信机房,酒店,民间信仰点,饭店,影剧院,福利院,卡拉ok厅,仓库,会计所,停车场,燃气调压站,餐厅,会堂,夜总会,物流中心,银行网点,车辆检修库,垃圾站（中转站）,茶馆,营业性室内健身,游艺厅,堆场,宠物医院,加油站,公共厕所,咖啡厅,学校,网吧,汽车服务店,高速服务区,数据中心,桑拿浴,托儿所,酒吧,污水处理设施,幼儿园,儿童游乐厅,室内儿童活动场所</t>
+    <t>住宅小区公共区域内场所，商场，公共图书馆，医院，歌舞厅，工业厂房，独立办公楼，民用机场航站楼，变电站，集体宿舍，寺庙，市场，博物馆，疗养院，
+录像厅，生产车间，商务公寓，客运车站候车厅，水泵房，宾馆，教堂，沿街商铺，公共展览馆，养老院，放映厅，加工场所，律所，客运码头候船厅，通信机房，酒店，民间信仰点，饭店，影剧院，福利院，卡拉ok厅，仓库，会计所，停车场，燃气调压站，餐厅，会堂，夜总会，物流中心，银行网点，车辆检修库，营业性室内健身，游艺厅，堆场，宠物医院，加油站，公共厕所，咖啡厅，学校，网吧，汽车服务店，高速服务区，数据中心，桑拿浴，托儿所，酒吧，污水处理设施，幼儿园，儿童游乐厅，室内儿童活动场所</t>
   </si>
   <si>
     <t>盈浦街道-城市运行管理中心</t>
@@ -816,14 +817,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1170,12 +1164,25 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1279,28 +1286,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1309,123 +1319,126 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1774,6 +1787,11 @@
   <sheetPr/>
   <dimension ref="A1:G137"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="18.712962962963" customWidth="1"/>
+    <col min="6" max="6" width="39.3981481481481" customWidth="1"/>
+    <col min="7" max="7" width="137.888888888889" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
@@ -3569,7 +3587,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" ht="105" customHeight="1" spans="1:7">
       <c r="A79" t="s">
         <v>134</v>
       </c>
@@ -3585,11 +3603,11 @@
       <c r="E79" t="s">
         <v>45</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="G79" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -4903,7 +4921,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" ht="106" customHeight="1" spans="1:7">
       <c r="A137" t="s">
         <v>219</v>
       </c>
